--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2262"/>
+  <dimension ref="A1:E2263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61490,6 +61490,33 @@
         </is>
       </c>
     </row>
+    <row r="2263">
+      <c r="A2263" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="B2263" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2263" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D2263" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E2263" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2263"/>
+  <dimension ref="A1:E2264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61517,6 +61517,33 @@
         </is>
       </c>
     </row>
+    <row r="2264">
+      <c r="A2264" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="B2264" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2264" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="D2264" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="E2264" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2264"/>
+  <dimension ref="A1:E2265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61544,6 +61544,33 @@
         </is>
       </c>
     </row>
+    <row r="2265">
+      <c r="A2265" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B2265" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2265" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D2265" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="E2265" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2265"/>
+  <dimension ref="A1:E2266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61571,6 +61571,33 @@
         </is>
       </c>
     </row>
+    <row r="2266">
+      <c r="A2266" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B2266" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2266" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D2266" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E2266" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2266"/>
+  <dimension ref="A1:E2267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61598,6 +61598,33 @@
         </is>
       </c>
     </row>
+    <row r="2267">
+      <c r="A2267" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B2267" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2267" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D2267" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="E2267" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2267"/>
+  <dimension ref="A1:E2268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61625,6 +61625,33 @@
         </is>
       </c>
     </row>
+    <row r="2268">
+      <c r="A2268" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B2268" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2268" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="D2268" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="E2268" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2268"/>
+  <dimension ref="A1:E2269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61652,6 +61652,33 @@
         </is>
       </c>
     </row>
+    <row r="2269">
+      <c r="A2269" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="B2269" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2269" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="D2269" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E2269" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2269"/>
+  <dimension ref="A1:E2270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61679,6 +61679,33 @@
         </is>
       </c>
     </row>
+    <row r="2270">
+      <c r="A2270" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="B2270" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2270" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D2270" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E2270" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2270"/>
+  <dimension ref="A1:E2271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61706,6 +61706,33 @@
         </is>
       </c>
     </row>
+    <row r="2271">
+      <c r="A2271" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B2271" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2271" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D2271" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E2271" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2271"/>
+  <dimension ref="A1:E2272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61733,6 +61733,33 @@
         </is>
       </c>
     </row>
+    <row r="2272">
+      <c r="A2272" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B2272" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2272" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D2272" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E2272" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2272"/>
+  <dimension ref="A1:E2273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61760,6 +61760,33 @@
         </is>
       </c>
     </row>
+    <row r="2273">
+      <c r="A2273" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B2273" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2273" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D2273" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E2273" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2273"/>
+  <dimension ref="A1:E2274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61787,6 +61787,33 @@
         </is>
       </c>
     </row>
+    <row r="2274">
+      <c r="A2274" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B2274" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2274" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D2274" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E2274" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2274"/>
+  <dimension ref="A1:E2275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61814,6 +61814,33 @@
         </is>
       </c>
     </row>
+    <row r="2275">
+      <c r="A2275" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B2275" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2275" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D2275" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E2275" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2275"/>
+  <dimension ref="A1:E2276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61841,6 +61841,33 @@
         </is>
       </c>
     </row>
+    <row r="2276">
+      <c r="A2276" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B2276" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2276" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D2276" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E2276" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2276"/>
+  <dimension ref="A1:E2277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61868,6 +61868,33 @@
         </is>
       </c>
     </row>
+    <row r="2277">
+      <c r="A2277" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B2277" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2277" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D2277" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E2277" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2277"/>
+  <dimension ref="A1:E2278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61895,6 +61895,33 @@
         </is>
       </c>
     </row>
+    <row r="2278">
+      <c r="A2278" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B2278" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2278" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D2278" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="E2278" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2278"/>
+  <dimension ref="A1:E2279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61922,6 +61922,33 @@
         </is>
       </c>
     </row>
+    <row r="2279">
+      <c r="A2279" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B2279" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2279" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D2279" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="E2279" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2279"/>
+  <dimension ref="A1:E2280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61949,6 +61949,33 @@
         </is>
       </c>
     </row>
+    <row r="2280">
+      <c r="A2280" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B2280" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2280" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D2280" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="E2280" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2280"/>
+  <dimension ref="A1:E2281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61976,6 +61976,33 @@
         </is>
       </c>
     </row>
+    <row r="2281">
+      <c r="A2281" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B2281" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2281" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D2281" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E2281" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2281"/>
+  <dimension ref="A1:E2282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62003,6 +62003,33 @@
         </is>
       </c>
     </row>
+    <row r="2282">
+      <c r="A2282" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B2282" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2282" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D2282" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E2282" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2282"/>
+  <dimension ref="A1:E2283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62030,6 +62030,33 @@
         </is>
       </c>
     </row>
+    <row r="2283">
+      <c r="A2283" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B2283" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2283" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D2283" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E2283" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2283"/>
+  <dimension ref="A1:E2284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62057,6 +62057,33 @@
         </is>
       </c>
     </row>
+    <row r="2284">
+      <c r="A2284" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B2284" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2284" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D2284" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E2284" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2284"/>
+  <dimension ref="A1:E2285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62084,6 +62084,33 @@
         </is>
       </c>
     </row>
+    <row r="2285">
+      <c r="A2285" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B2285" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2285" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D2285" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E2285" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2285"/>
+  <dimension ref="A1:E2286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62111,6 +62111,33 @@
         </is>
       </c>
     </row>
+    <row r="2286">
+      <c r="A2286" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B2286" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2286" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D2286" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E2286" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2286"/>
+  <dimension ref="A1:E2287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62138,6 +62138,33 @@
         </is>
       </c>
     </row>
+    <row r="2287">
+      <c r="A2287" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B2287" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2287" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D2287" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E2287" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2287"/>
+  <dimension ref="A1:E2288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62165,6 +62165,33 @@
         </is>
       </c>
     </row>
+    <row r="2288">
+      <c r="A2288" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B2288" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2288" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="D2288" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E2288" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2288"/>
+  <dimension ref="A1:E2289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62192,6 +62192,33 @@
         </is>
       </c>
     </row>
+    <row r="2289">
+      <c r="A2289" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B2289" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2289" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D2289" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E2289" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2289"/>
+  <dimension ref="A1:E2290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62219,6 +62219,33 @@
         </is>
       </c>
     </row>
+    <row r="2290">
+      <c r="A2290" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B2290" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2290" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D2290" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E2290" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2290"/>
+  <dimension ref="A1:E2291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62246,6 +62246,33 @@
         </is>
       </c>
     </row>
+    <row r="2291">
+      <c r="A2291" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B2291" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2291" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D2291" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="E2291" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2291"/>
+  <dimension ref="A1:E2292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62273,6 +62273,33 @@
         </is>
       </c>
     </row>
+    <row r="2292">
+      <c r="A2292" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B2292" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2292" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D2292" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E2292" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2292"/>
+  <dimension ref="A1:E2293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62300,6 +62300,33 @@
         </is>
       </c>
     </row>
+    <row r="2293">
+      <c r="A2293" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B2293" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2293" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D2293" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="E2293" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2293"/>
+  <dimension ref="A1:E2294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62327,6 +62327,33 @@
         </is>
       </c>
     </row>
+    <row r="2294">
+      <c r="A2294" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B2294" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2294" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D2294" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="E2294" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2294"/>
+  <dimension ref="A1:E2295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62354,6 +62354,33 @@
         </is>
       </c>
     </row>
+    <row r="2295">
+      <c r="A2295" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B2295" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2295" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D2295" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E2295" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2295"/>
+  <dimension ref="A1:E2296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62381,6 +62381,33 @@
         </is>
       </c>
     </row>
+    <row r="2296">
+      <c r="A2296" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B2296" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2296" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D2296" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="E2296" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2296"/>
+  <dimension ref="A1:E2297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62408,6 +62408,33 @@
         </is>
       </c>
     </row>
+    <row r="2297">
+      <c r="A2297" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B2297" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2297" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D2297" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E2297" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2297"/>
+  <dimension ref="A1:E2298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62435,6 +62435,33 @@
         </is>
       </c>
     </row>
+    <row r="2298">
+      <c r="A2298" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B2298" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2298" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D2298" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E2298" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2298"/>
+  <dimension ref="A1:E2299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62462,6 +62462,33 @@
         </is>
       </c>
     </row>
+    <row r="2299">
+      <c r="A2299" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B2299" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2299" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D2299" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="E2299" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2299"/>
+  <dimension ref="A1:E2300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62489,6 +62489,33 @@
         </is>
       </c>
     </row>
+    <row r="2300">
+      <c r="A2300" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B2300" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2300" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D2300" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E2300" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2300"/>
+  <dimension ref="A1:E2301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62516,6 +62516,33 @@
         </is>
       </c>
     </row>
+    <row r="2301">
+      <c r="A2301" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B2301" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2301" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D2301" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E2301" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2301"/>
+  <dimension ref="A1:E2302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62543,6 +62543,33 @@
         </is>
       </c>
     </row>
+    <row r="2302">
+      <c r="A2302" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B2302" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2302" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D2302" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E2302" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2302"/>
+  <dimension ref="A1:E2303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62570,6 +62570,33 @@
         </is>
       </c>
     </row>
+    <row r="2303">
+      <c r="A2303" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B2303" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2303" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="D2303" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="E2303" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2303"/>
+  <dimension ref="A1:E2304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62597,6 +62597,33 @@
         </is>
       </c>
     </row>
+    <row r="2304">
+      <c r="A2304" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B2304" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2304" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D2304" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E2304" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2304"/>
+  <dimension ref="A1:E2305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62624,6 +62624,33 @@
         </is>
       </c>
     </row>
+    <row r="2305">
+      <c r="A2305" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B2305" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2305" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D2305" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="E2305" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2305"/>
+  <dimension ref="A1:E2306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62651,6 +62651,33 @@
         </is>
       </c>
     </row>
+    <row r="2306">
+      <c r="A2306" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B2306" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2306" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D2306" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="E2306" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2306"/>
+  <dimension ref="A1:E2307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62678,6 +62678,33 @@
         </is>
       </c>
     </row>
+    <row r="2307">
+      <c r="A2307" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B2307" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2307" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D2307" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E2307" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2307"/>
+  <dimension ref="A1:E2308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62705,6 +62705,33 @@
         </is>
       </c>
     </row>
+    <row r="2308">
+      <c r="A2308" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B2308" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2308" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D2308" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="E2308" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2308"/>
+  <dimension ref="A1:E2309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62732,6 +62732,33 @@
         </is>
       </c>
     </row>
+    <row r="2309">
+      <c r="A2309" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B2309" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2309" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D2309" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="E2309" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2309"/>
+  <dimension ref="A1:E2310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62759,6 +62759,33 @@
         </is>
       </c>
     </row>
+    <row r="2310">
+      <c r="A2310" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B2310" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2310" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D2310" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E2310" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2310"/>
+  <dimension ref="A1:E2311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62786,6 +62786,33 @@
         </is>
       </c>
     </row>
+    <row r="2311">
+      <c r="A2311" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B2311" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2311" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D2311" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E2311" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2311"/>
+  <dimension ref="A1:E2312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62813,6 +62813,33 @@
         </is>
       </c>
     </row>
+    <row r="2312">
+      <c r="A2312" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B2312" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2312" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D2312" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="E2312" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2312"/>
+  <dimension ref="A1:E2313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62840,6 +62840,33 @@
         </is>
       </c>
     </row>
+    <row r="2313">
+      <c r="A2313" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B2313" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2313" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D2313" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="E2313" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2313"/>
+  <dimension ref="A1:E2314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62867,6 +62867,33 @@
         </is>
       </c>
     </row>
+    <row r="2314">
+      <c r="A2314" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B2314" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2314" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D2314" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E2314" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2314"/>
+  <dimension ref="A1:E2315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62894,6 +62894,33 @@
         </is>
       </c>
     </row>
+    <row r="2315">
+      <c r="A2315" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B2315" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2315" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D2315" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="E2315" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2315"/>
+  <dimension ref="A1:E2316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62921,6 +62921,33 @@
         </is>
       </c>
     </row>
+    <row r="2316">
+      <c r="A2316" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B2316" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2316" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D2316" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="E2316" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2316"/>
+  <dimension ref="A1:E2317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62948,6 +62948,33 @@
         </is>
       </c>
     </row>
+    <row r="2317">
+      <c r="A2317" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B2317" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2317" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D2317" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E2317" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2317"/>
+  <dimension ref="A1:E2318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62975,6 +62975,33 @@
         </is>
       </c>
     </row>
+    <row r="2318">
+      <c r="A2318" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B2318" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2318" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D2318" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E2318" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2318"/>
+  <dimension ref="A1:E2319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63002,6 +63002,33 @@
         </is>
       </c>
     </row>
+    <row r="2319">
+      <c r="A2319" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B2319" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2319" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D2319" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E2319" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2319"/>
+  <dimension ref="A1:E2320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63029,6 +63029,33 @@
         </is>
       </c>
     </row>
+    <row r="2320">
+      <c r="A2320" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B2320" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2320" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D2320" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E2320" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2320"/>
+  <dimension ref="A1:E2321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63056,6 +63056,33 @@
         </is>
       </c>
     </row>
+    <row r="2321">
+      <c r="A2321" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B2321" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2321" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D2321" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E2321" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2321"/>
+  <dimension ref="A1:E2322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63083,6 +63083,33 @@
         </is>
       </c>
     </row>
+    <row r="2322">
+      <c r="A2322" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B2322" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2322" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D2322" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="E2322" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2322"/>
+  <dimension ref="A1:E2323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63110,6 +63110,33 @@
         </is>
       </c>
     </row>
+    <row r="2323">
+      <c r="A2323" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B2323" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2323" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D2323" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E2323" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2323"/>
+  <dimension ref="A1:E2324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63137,6 +63137,33 @@
         </is>
       </c>
     </row>
+    <row r="2324">
+      <c r="A2324" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B2324" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2324" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D2324" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E2324" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2324"/>
+  <dimension ref="A1:E2325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63164,6 +63164,33 @@
         </is>
       </c>
     </row>
+    <row r="2325">
+      <c r="A2325" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B2325" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2325" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D2325" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E2325" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2325"/>
+  <dimension ref="A1:E2326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63191,6 +63191,33 @@
         </is>
       </c>
     </row>
+    <row r="2326">
+      <c r="A2326" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B2326" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2326" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D2326" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E2326" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2326"/>
+  <dimension ref="A1:E2327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63218,6 +63218,33 @@
         </is>
       </c>
     </row>
+    <row r="2327">
+      <c r="A2327" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B2327" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2327" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D2327" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E2327" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2327"/>
+  <dimension ref="A1:E2328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63245,6 +63245,33 @@
         </is>
       </c>
     </row>
+    <row r="2328">
+      <c r="A2328" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B2328" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2328" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D2328" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="E2328" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2328"/>
+  <dimension ref="A1:E2329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63272,6 +63272,33 @@
         </is>
       </c>
     </row>
+    <row r="2329">
+      <c r="A2329" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B2329" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2329" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D2329" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="E2329" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2329"/>
+  <dimension ref="A1:E2330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63299,6 +63299,33 @@
         </is>
       </c>
     </row>
+    <row r="2330">
+      <c r="A2330" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B2330" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2330" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D2330" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="E2330" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2330"/>
+  <dimension ref="A1:E2331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63326,6 +63326,33 @@
         </is>
       </c>
     </row>
+    <row r="2331">
+      <c r="A2331" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B2331" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2331" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D2331" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E2331" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2331"/>
+  <dimension ref="A1:E2332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63353,6 +63353,33 @@
         </is>
       </c>
     </row>
+    <row r="2332">
+      <c r="A2332" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B2332" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2332" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D2332" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E2332" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2332"/>
+  <dimension ref="A1:E2333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63380,6 +63380,33 @@
         </is>
       </c>
     </row>
+    <row r="2333">
+      <c r="A2333" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B2333" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2333" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D2333" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="E2333" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2333"/>
+  <dimension ref="A1:E2334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63407,6 +63407,33 @@
         </is>
       </c>
     </row>
+    <row r="2334">
+      <c r="A2334" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B2334" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2334" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D2334" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E2334" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2334"/>
+  <dimension ref="A1:E2335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63434,6 +63434,33 @@
         </is>
       </c>
     </row>
+    <row r="2335">
+      <c r="A2335" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B2335" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2335" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D2335" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E2335" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2335"/>
+  <dimension ref="A1:E2336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63461,6 +63461,33 @@
         </is>
       </c>
     </row>
+    <row r="2336">
+      <c r="A2336" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B2336" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2336" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D2336" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="E2336" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2336"/>
+  <dimension ref="A1:E2337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63488,6 +63488,33 @@
         </is>
       </c>
     </row>
+    <row r="2337">
+      <c r="A2337" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B2337" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2337" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="D2337" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="E2337" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2337"/>
+  <dimension ref="A1:E2338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63515,6 +63515,33 @@
         </is>
       </c>
     </row>
+    <row r="2338">
+      <c r="A2338" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B2338" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2338" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D2338" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="E2338" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2338"/>
+  <dimension ref="A1:E2339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63542,6 +63542,33 @@
         </is>
       </c>
     </row>
+    <row r="2339">
+      <c r="A2339" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B2339" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2339" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D2339" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="E2339" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2339"/>
+  <dimension ref="A1:E2340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63569,6 +63569,33 @@
         </is>
       </c>
     </row>
+    <row r="2340">
+      <c r="A2340" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B2340" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2340" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D2340" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="E2340" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2340"/>
+  <dimension ref="A1:E2341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63596,6 +63596,33 @@
         </is>
       </c>
     </row>
+    <row r="2341">
+      <c r="A2341" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B2341" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2341" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D2341" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E2341" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2341"/>
+  <dimension ref="A1:E2342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63623,6 +63623,33 @@
         </is>
       </c>
     </row>
+    <row r="2342">
+      <c r="A2342" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B2342" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2342" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D2342" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="E2342" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2342"/>
+  <dimension ref="A1:E2343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63650,6 +63650,33 @@
         </is>
       </c>
     </row>
+    <row r="2343">
+      <c r="A2343" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B2343" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2343" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D2343" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="E2343" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2343"/>
+  <dimension ref="A1:E2344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63677,6 +63677,33 @@
         </is>
       </c>
     </row>
+    <row r="2344">
+      <c r="A2344" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B2344" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2344" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D2344" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E2344" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2344"/>
+  <dimension ref="A1:E2345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63704,6 +63704,33 @@
         </is>
       </c>
     </row>
+    <row r="2345">
+      <c r="A2345" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B2345" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2345" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D2345" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E2345" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2345"/>
+  <dimension ref="A1:E2346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63731,6 +63731,33 @@
         </is>
       </c>
     </row>
+    <row r="2346">
+      <c r="A2346" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B2346" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2346" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D2346" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E2346" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2346"/>
+  <dimension ref="A1:E2347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63758,6 +63758,33 @@
         </is>
       </c>
     </row>
+    <row r="2347">
+      <c r="A2347" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B2347" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2347" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D2347" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E2347" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2347"/>
+  <dimension ref="A1:E2348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63785,6 +63785,33 @@
         </is>
       </c>
     </row>
+    <row r="2348">
+      <c r="A2348" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B2348" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2348" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D2348" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E2348" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2348"/>
+  <dimension ref="A1:E2350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63812,6 +63812,60 @@
         </is>
       </c>
     </row>
+    <row r="2349">
+      <c r="A2349" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B2349" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2349" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D2349" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E2349" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
+    <row r="2350">
+      <c r="A2350" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B2350" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2350" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D2350" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E2350" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2350"/>
+  <dimension ref="A1:E2351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63866,6 +63866,33 @@
         </is>
       </c>
     </row>
+    <row r="2351">
+      <c r="A2351" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B2351" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2351" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D2351" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="E2351" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2351"/>
+  <dimension ref="A1:E2352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63893,6 +63893,33 @@
         </is>
       </c>
     </row>
+    <row r="2352">
+      <c r="A2352" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B2352" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2352" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D2352" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E2352" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2352"/>
+  <dimension ref="A1:E2353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63920,6 +63920,33 @@
         </is>
       </c>
     </row>
+    <row r="2353">
+      <c r="A2353" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B2353" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2353" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D2353" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E2353" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2353"/>
+  <dimension ref="A1:E2354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63947,6 +63947,33 @@
         </is>
       </c>
     </row>
+    <row r="2354">
+      <c r="A2354" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B2354" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2354" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D2354" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="E2354" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2354"/>
+  <dimension ref="A1:E2355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63974,6 +63974,33 @@
         </is>
       </c>
     </row>
+    <row r="2355">
+      <c r="A2355" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B2355" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2355" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D2355" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="E2355" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2355"/>
+  <dimension ref="A1:E2356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64001,6 +64001,33 @@
         </is>
       </c>
     </row>
+    <row r="2356">
+      <c r="A2356" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B2356" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2356" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D2356" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E2356" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2356"/>
+  <dimension ref="A1:E2357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64028,6 +64028,33 @@
         </is>
       </c>
     </row>
+    <row r="2357">
+      <c r="A2357" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B2357" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2357" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D2357" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="E2357" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2357"/>
+  <dimension ref="A1:E2358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64055,6 +64055,33 @@
         </is>
       </c>
     </row>
+    <row r="2358">
+      <c r="A2358" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B2358" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2358" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D2358" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E2358" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2358"/>
+  <dimension ref="A1:E2359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64082,6 +64082,33 @@
         </is>
       </c>
     </row>
+    <row r="2359">
+      <c r="A2359" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B2359" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2359" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D2359" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E2359" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2359"/>
+  <dimension ref="A1:E2360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64109,6 +64109,33 @@
         </is>
       </c>
     </row>
+    <row r="2360">
+      <c r="A2360" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B2360" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2360" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D2360" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E2360" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2360"/>
+  <dimension ref="A1:E2361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64136,6 +64136,33 @@
         </is>
       </c>
     </row>
+    <row r="2361">
+      <c r="A2361" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B2361" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2361" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="D2361" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E2361" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2361"/>
+  <dimension ref="A1:E2362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64163,6 +64163,33 @@
         </is>
       </c>
     </row>
+    <row r="2362">
+      <c r="A2362" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B2362" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2362" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D2362" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E2362" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2362"/>
+  <dimension ref="A1:E2363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64190,6 +64190,33 @@
         </is>
       </c>
     </row>
+    <row r="2363">
+      <c r="A2363" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B2363" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2363" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D2363" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E2363" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2363"/>
+  <dimension ref="A1:E2364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64217,6 +64217,33 @@
         </is>
       </c>
     </row>
+    <row r="2364">
+      <c r="A2364" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B2364" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2364" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D2364" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E2364" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2364"/>
+  <dimension ref="A1:E2365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64244,6 +64244,33 @@
         </is>
       </c>
     </row>
+    <row r="2365">
+      <c r="A2365" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B2365" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2365" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="D2365" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="E2365" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2365"/>
+  <dimension ref="A1:E2366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64271,6 +64271,33 @@
         </is>
       </c>
     </row>
+    <row r="2366">
+      <c r="A2366" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B2366" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2366" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D2366" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E2366" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2366"/>
+  <dimension ref="A1:E2367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64298,6 +64298,33 @@
         </is>
       </c>
     </row>
+    <row r="2367">
+      <c r="A2367" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B2367" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2367" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D2367" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E2367" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2367"/>
+  <dimension ref="A1:E2368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64325,6 +64325,33 @@
         </is>
       </c>
     </row>
+    <row r="2368">
+      <c r="A2368" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B2368" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2368" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D2368" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="E2368" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2368"/>
+  <dimension ref="A1:E2369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64352,6 +64352,33 @@
         </is>
       </c>
     </row>
+    <row r="2369">
+      <c r="A2369" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B2369" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2369" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D2369" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="E2369" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2369"/>
+  <dimension ref="A1:E2370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64379,6 +64379,33 @@
         </is>
       </c>
     </row>
+    <row r="2370">
+      <c r="A2370" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B2370" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2370" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D2370" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="E2370" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2370"/>
+  <dimension ref="A1:E2371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64406,6 +64406,33 @@
         </is>
       </c>
     </row>
+    <row r="2371">
+      <c r="A2371" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B2371" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2371" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D2371" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E2371" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2371"/>
+  <dimension ref="A1:E2372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64433,6 +64433,33 @@
         </is>
       </c>
     </row>
+    <row r="2372">
+      <c r="A2372" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B2372" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2372" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D2372" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E2372" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2372"/>
+  <dimension ref="A1:E2373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64460,6 +64460,33 @@
         </is>
       </c>
     </row>
+    <row r="2373">
+      <c r="A2373" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B2373" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2373" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D2373" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E2373" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2373"/>
+  <dimension ref="A1:E2374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64487,6 +64487,33 @@
         </is>
       </c>
     </row>
+    <row r="2374">
+      <c r="A2374" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B2374" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2374" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D2374" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="E2374" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2374"/>
+  <dimension ref="A1:E2375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64514,6 +64514,33 @@
         </is>
       </c>
     </row>
+    <row r="2375">
+      <c r="A2375" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B2375" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2375" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D2375" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E2375" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2375"/>
+  <dimension ref="A1:E2376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64541,6 +64541,33 @@
         </is>
       </c>
     </row>
+    <row r="2376">
+      <c r="A2376" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B2376" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2376" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D2376" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="E2376" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2376"/>
+  <dimension ref="A1:E2377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64568,6 +64568,33 @@
         </is>
       </c>
     </row>
+    <row r="2377">
+      <c r="A2377" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B2377" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2377" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D2377" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="E2377" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2377"/>
+  <dimension ref="A1:E2378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64595,6 +64595,33 @@
         </is>
       </c>
     </row>
+    <row r="2378">
+      <c r="A2378" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B2378" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2378" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D2378" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E2378" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2378"/>
+  <dimension ref="A1:E2379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64622,6 +64622,33 @@
         </is>
       </c>
     </row>
+    <row r="2379">
+      <c r="A2379" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B2379" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2379" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D2379" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="E2379" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2379"/>
+  <dimension ref="A1:E2380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64649,6 +64649,33 @@
         </is>
       </c>
     </row>
+    <row r="2380">
+      <c r="A2380" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B2380" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2380" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D2380" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="E2380" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2380"/>
+  <dimension ref="A1:E2381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64676,6 +64676,33 @@
         </is>
       </c>
     </row>
+    <row r="2381">
+      <c r="A2381" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B2381" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2381" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D2381" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E2381" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2381"/>
+  <dimension ref="A1:E2382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64703,6 +64703,33 @@
         </is>
       </c>
     </row>
+    <row r="2382">
+      <c r="A2382" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B2382" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2382" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D2382" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E2382" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2382"/>
+  <dimension ref="A1:E2383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64730,6 +64730,33 @@
         </is>
       </c>
     </row>
+    <row r="2383">
+      <c r="A2383" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B2383" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2383" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D2383" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E2383" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2383"/>
+  <dimension ref="A1:E2384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64757,6 +64757,33 @@
         </is>
       </c>
     </row>
+    <row r="2384">
+      <c r="A2384" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B2384" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2384" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D2384" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E2384" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2384"/>
+  <dimension ref="A1:E2385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64784,6 +64784,33 @@
         </is>
       </c>
     </row>
+    <row r="2385">
+      <c r="A2385" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B2385" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2385" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D2385" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E2385" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2385"/>
+  <dimension ref="A1:E2386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64811,6 +64811,33 @@
         </is>
       </c>
     </row>
+    <row r="2386">
+      <c r="A2386" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B2386" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2386" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D2386" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E2386" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2386"/>
+  <dimension ref="A1:E2387"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64838,6 +64838,33 @@
         </is>
       </c>
     </row>
+    <row r="2387">
+      <c r="A2387" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B2387" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2387" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D2387" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="E2387" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2387"/>
+  <dimension ref="A1:E2388"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64865,6 +64865,33 @@
         </is>
       </c>
     </row>
+    <row r="2388">
+      <c r="A2388" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B2388" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2388" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D2388" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E2388" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2388"/>
+  <dimension ref="A1:E2389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64892,6 +64892,33 @@
         </is>
       </c>
     </row>
+    <row r="2389">
+      <c r="A2389" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B2389" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2389" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D2389" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="E2389" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2389"/>
+  <dimension ref="A1:E2390"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64919,6 +64919,33 @@
         </is>
       </c>
     </row>
+    <row r="2390">
+      <c r="A2390" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B2390" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2390" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D2390" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E2390" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2390"/>
+  <dimension ref="A1:E2391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64946,6 +64946,33 @@
         </is>
       </c>
     </row>
+    <row r="2391">
+      <c r="A2391" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B2391" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2391" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D2391" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E2391" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2391"/>
+  <dimension ref="A1:E2392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64973,6 +64973,33 @@
         </is>
       </c>
     </row>
+    <row r="2392">
+      <c r="A2392" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B2392" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2392" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D2392" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="E2392" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2392"/>
+  <dimension ref="A1:E2393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65000,6 +65000,33 @@
         </is>
       </c>
     </row>
+    <row r="2393">
+      <c r="A2393" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B2393" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2393" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D2393" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E2393" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2393"/>
+  <dimension ref="A1:E2394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65027,6 +65027,33 @@
         </is>
       </c>
     </row>
+    <row r="2394">
+      <c r="A2394" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B2394" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2394" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="D2394" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="E2394" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2394"/>
+  <dimension ref="A1:E2395"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65054,6 +65054,33 @@
         </is>
       </c>
     </row>
+    <row r="2395">
+      <c r="A2395" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B2395" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2395" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D2395" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E2395" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2395"/>
+  <dimension ref="A1:E2396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65081,6 +65081,33 @@
         </is>
       </c>
     </row>
+    <row r="2396">
+      <c r="A2396" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B2396" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2396" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D2396" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E2396" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2396"/>
+  <dimension ref="A1:E2397"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65108,6 +65108,33 @@
         </is>
       </c>
     </row>
+    <row r="2397">
+      <c r="A2397" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B2397" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2397" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D2397" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="E2397" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2397"/>
+  <dimension ref="A1:E2398"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65135,6 +65135,33 @@
         </is>
       </c>
     </row>
+    <row r="2398">
+      <c r="A2398" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B2398" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2398" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D2398" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E2398" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2398"/>
+  <dimension ref="A1:E2399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65162,6 +65162,33 @@
         </is>
       </c>
     </row>
+    <row r="2399">
+      <c r="A2399" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B2399" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2399" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D2399" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E2399" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2399"/>
+  <dimension ref="A1:E2400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65189,6 +65189,33 @@
         </is>
       </c>
     </row>
+    <row r="2400">
+      <c r="A2400" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B2400" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2400" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D2400" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="E2400" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2400"/>
+  <dimension ref="A1:E2401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65216,6 +65216,33 @@
         </is>
       </c>
     </row>
+    <row r="2401">
+      <c r="A2401" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2401" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2401" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D2401" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="E2401" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2401"/>
+  <dimension ref="A1:E2402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65243,6 +65243,33 @@
         </is>
       </c>
     </row>
+    <row r="2402">
+      <c r="A2402" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2402" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2402" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D2402" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E2402" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,31 +425,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2446"/>
+  <dimension ref="A1:E2447"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>sorteo</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>primero</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>segundo</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>tercero</t>
         </is>
@@ -66455,6 +66467,33 @@
       <c r="E2446" t="inlineStr">
         <is>
           <t>62</t>
+        </is>
+      </c>
+    </row>
+    <row r="2447">
+      <c r="A2447" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2447" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2447" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D2447" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="E2447" t="inlineStr">
+        <is>
+          <t>16</t>
         </is>
       </c>
     </row>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2462"/>
+  <dimension ref="A1:E2463"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66890,6 +66890,33 @@
         </is>
       </c>
     </row>
+    <row r="2463">
+      <c r="A2463" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B2463" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2463" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D2463" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E2463" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2463"/>
+  <dimension ref="A1:E2464"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66917,6 +66917,33 @@
         </is>
       </c>
     </row>
+    <row r="2464">
+      <c r="A2464" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B2464" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2464" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D2464" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E2464" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2632"/>
+  <dimension ref="A1:E2634"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71480,6 +71480,60 @@
         </is>
       </c>
     </row>
+    <row r="2633">
+      <c r="A2633" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B2633" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2633" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D2633" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="E2633" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+    </row>
+    <row r="2634">
+      <c r="A2634" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B2634" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2634" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D2634" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E2634" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2658"/>
+  <dimension ref="A1:E2660"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72182,6 +72182,60 @@
         </is>
       </c>
     </row>
+    <row r="2659">
+      <c r="A2659" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B2659" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2659" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D2659" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E2659" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+    </row>
+    <row r="2660">
+      <c r="A2660" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B2660" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2660" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D2660" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="E2660" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
